--- a/HR-Reachout-Agent-main/WhatsApp_Leads.xlsx
+++ b/HR-Reachout-Agent-main/WhatsApp_Leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,38 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>['User is interested in learning about the services offered by the app.', 'User wants to know how to use the app effectively.', 'User has tested the app and found it awesome.', 'User is interested in a personalized demo from the team.']</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-20T03:39:56.898302</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>whatsapp_3913947408901407_1054801481058488_916206535856</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>916206535856</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ashutosh Pandey</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>aspandey1904@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>['User wants to book an appointment.', 'User has selected Monday, 25 May 2026.', 'User provided their name and email for the appointment.']</t>
         </is>
       </c>
     </row>

--- a/HR-Reachout-Agent-main/WhatsApp_Leads.xlsx
+++ b/HR-Reachout-Agent-main/WhatsApp_Leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,38 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>['User wants to book an appointment.', 'User has selected Monday, 25 May 2026.', 'User provided their name and email for the appointment.']</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:30:21.797711</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>whatsapp_981276181065714_1072900375915131_916206535856</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>916206535856</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ashutosh Pandey</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ssquarefitnessclubpune@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>['User is interested in membership plans offered by S Square Fitness.', 'User wants to know the location of the gym.', 'User inquired about booking a visit to the gym.']</t>
         </is>
       </c>
     </row>
